--- a/HotGuy/Assets/Config/Excel/SCTaskQuoteConfig.xlsx
+++ b/HotGuy/Assets/Config/Excel/SCTaskQuoteConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GP\GP-TestRepo\HotGuy\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D25B8FC-15E7-43CF-86CD-A108B8FE1914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EF0FE9-E4C6-4425-89C7-73026CA259F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="14400" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1073" yWindow="1073" windowWidth="14400" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConstConfig" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,8 @@
     <t>听我的，上</t>
   </si>
   <si>
-    <t>给小比尝尝这个口味</t>
+    <t>给小比尝尝这款</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
